--- a/res/tabela da comunidade.xlsx
+++ b/res/tabela da comunidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_Zoo-Rebio/ZooRebio3-23_24/rebio23-part/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_B992312702B166F0E476389F13FD156A6ADA3413" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED89D97A-0757-40C1-8C82-90E4A58F0585}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_B992312702B166F0E476389F13FD156A6ADA3413" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6581421A-5591-4556-A5C5-D1B7D845147B}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-12465" windowWidth="22335" windowHeight="27945" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-22425" windowWidth="21840" windowHeight="37920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3658" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="182">
   <si>
     <t>Variable</t>
   </si>
@@ -501,6 +501,72 @@
   </si>
   <si>
     <t>Tri.tetractis</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>Wet</t>
+  </si>
+  <si>
+    <t>Dry</t>
+  </si>
+  <si>
+    <t>Ponto10</t>
+  </si>
+  <si>
+    <t>Ponto5</t>
+  </si>
+  <si>
+    <t>Ponto6</t>
+  </si>
+  <si>
+    <t>Ponto7</t>
+  </si>
+  <si>
+    <t>Ponto8</t>
+  </si>
+  <si>
+    <t>Ponto9</t>
+  </si>
+  <si>
+    <t>Ponto12</t>
+  </si>
+  <si>
+    <t>Ponto13</t>
+  </si>
+  <si>
+    <t>Ponto14</t>
+  </si>
+  <si>
+    <t>Ponto15</t>
+  </si>
+  <si>
+    <t>Ponto16</t>
+  </si>
+  <si>
+    <t>Ponto17</t>
+  </si>
+  <si>
+    <t>Ponto18</t>
+  </si>
+  <si>
+    <t>Ponto19</t>
+  </si>
+  <si>
+    <t>Ponto20</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Barro Branco Stream</t>
+  </si>
+  <si>
+    <t>Caiana Stream</t>
   </si>
 </sst>
 </file>
@@ -536,8 +602,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,6 +628,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6450,300 +6529,192 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{768C672F-8BDD-430E-9621-0F0E0D5E9FE7}">
-  <dimension ref="A1:AE59"/>
+  <dimension ref="A1:AE61"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>30</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>33</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>173</v>
       </c>
       <c r="R3" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="V3" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="W3" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="X3" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
       <c r="Y3" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="Z3" t="s">
-        <v>33</v>
+        <v>173</v>
       </c>
       <c r="AA3" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="AB3" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="AC3" t="s">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="AD3" t="s">
-        <v>33</v>
+        <v>177</v>
       </c>
       <c r="AE3" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -6752,13 +6723,13 @@
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
         <v>33</v>
@@ -6770,7 +6741,7 @@
         <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L4" t="s">
         <v>33</v>
@@ -6779,25 +6750,25 @@
         <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="s">
         <v>33</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U4" t="s">
         <v>33</v>
@@ -6835,102 +6806,102 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="M5" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="N5" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="R5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="T5" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="U5" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="V5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="X5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="Z5" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="AA5" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="AB5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="AC5" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="AD5" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="AE5" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -6942,13 +6913,13 @@
         <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
@@ -6981,10 +6952,10 @@
         <v>33</v>
       </c>
       <c r="R6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="S6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T6" t="s">
         <v>33</v>
@@ -7025,102 +6996,102 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="O7" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="S7" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="U7" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="V7" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="W7" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="X7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="Z7" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="AA7" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="AC7" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="AD7" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="AE7" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -7171,10 +7142,10 @@
         <v>33</v>
       </c>
       <c r="R8" t="s">
+        <v>55</v>
+      </c>
+      <c r="S8" t="s">
         <v>35</v>
-      </c>
-      <c r="S8" t="s">
-        <v>33</v>
       </c>
       <c r="T8" t="s">
         <v>33</v>
@@ -7215,25 +7186,25 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
         <v>33</v>
@@ -7248,31 +7219,31 @@
         <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="M9" t="s">
         <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O9" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="P9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q9" t="s">
         <v>33</v>
       </c>
       <c r="R9" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T9" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="U9" t="s">
         <v>33</v>
@@ -7281,7 +7252,7 @@
         <v>33</v>
       </c>
       <c r="W9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="X9" t="s">
         <v>33</v>
@@ -7290,30 +7261,30 @@
         <v>33</v>
       </c>
       <c r="Z9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="AA9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AB9" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="AC9" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="AD9" t="s">
         <v>33</v>
       </c>
       <c r="AE9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -7325,7 +7296,7 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -7361,13 +7332,13 @@
         <v>33</v>
       </c>
       <c r="R10" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="T10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U10" t="s">
         <v>33</v>
@@ -7405,25 +7376,25 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -7435,7 +7406,7 @@
         <v>33</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s">
         <v>33</v>
@@ -7444,25 +7415,25 @@
         <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O11" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
         <v>33</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="S11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="U11" t="s">
         <v>33</v>
@@ -7471,7 +7442,7 @@
         <v>33</v>
       </c>
       <c r="W11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="X11" t="s">
         <v>33</v>
@@ -7480,30 +7451,30 @@
         <v>33</v>
       </c>
       <c r="Z11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="AC11" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="AD11" t="s">
         <v>33</v>
       </c>
       <c r="AE11" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
@@ -7512,13 +7483,13 @@
         <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
         <v>33</v>
@@ -7545,7 +7516,7 @@
         <v>33</v>
       </c>
       <c r="P12" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q12" t="s">
         <v>33</v>
@@ -7554,11 +7525,11 @@
         <v>88</v>
       </c>
       <c r="S12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T12" t="s">
         <v>35</v>
       </c>
-      <c r="T12" t="s">
-        <v>41</v>
-      </c>
       <c r="U12" t="s">
         <v>33</v>
       </c>
@@ -7578,7 +7549,7 @@
         <v>33</v>
       </c>
       <c r="AA12" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="AB12" t="s">
         <v>33</v>
@@ -7595,7 +7566,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -7673,7 +7644,7 @@
         <v>33</v>
       </c>
       <c r="AA13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="AB13" t="s">
         <v>33</v>
@@ -7690,7 +7661,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -7702,13 +7673,13 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
         <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
@@ -7735,19 +7706,19 @@
         <v>33</v>
       </c>
       <c r="P14" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="s">
         <v>33</v>
       </c>
       <c r="R14" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="S14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T14" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="U14" t="s">
         <v>33</v>
@@ -7768,7 +7739,7 @@
         <v>33</v>
       </c>
       <c r="AA14" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="AB14" t="s">
         <v>33</v>
@@ -7785,7 +7756,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -7863,7 +7834,7 @@
         <v>33</v>
       </c>
       <c r="AA15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AB15" t="s">
         <v>33</v>
@@ -7880,7 +7851,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
@@ -7975,10 +7946,10 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -8026,7 +7997,7 @@
         <v>33</v>
       </c>
       <c r="R17" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -8070,7 +8041,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -8121,10 +8092,10 @@
         <v>33</v>
       </c>
       <c r="R18" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T18" t="s">
         <v>33</v>
@@ -8165,7 +8136,7 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -8180,13 +8151,13 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="I19" t="s">
         <v>33</v>
@@ -8198,7 +8169,7 @@
         <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M19" t="s">
         <v>33</v>
@@ -8216,7 +8187,7 @@
         <v>33</v>
       </c>
       <c r="R19" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -8231,7 +8202,7 @@
         <v>33</v>
       </c>
       <c r="W19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X19" t="s">
         <v>33</v>
@@ -8243,7 +8214,7 @@
         <v>33</v>
       </c>
       <c r="AA19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AB19" t="s">
         <v>33</v>
@@ -8260,7 +8231,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
@@ -8311,7 +8282,7 @@
         <v>33</v>
       </c>
       <c r="R20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S20" t="s">
         <v>35</v>
@@ -8355,7 +8326,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
@@ -8367,7 +8338,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
         <v>33</v>
@@ -8376,7 +8347,7 @@
         <v>33</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I21" t="s">
         <v>33</v>
@@ -8385,13 +8356,13 @@
         <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L21" t="s">
         <v>33</v>
       </c>
       <c r="M21" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -8406,34 +8377,34 @@
         <v>33</v>
       </c>
       <c r="R21" t="s">
+        <v>38</v>
+      </c>
+      <c r="S21" t="s">
+        <v>33</v>
+      </c>
+      <c r="T21" t="s">
+        <v>33</v>
+      </c>
+      <c r="U21" t="s">
+        <v>33</v>
+      </c>
+      <c r="V21" t="s">
+        <v>33</v>
+      </c>
+      <c r="W21" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA21" t="s">
         <v>35</v>
-      </c>
-      <c r="S21" t="s">
-        <v>33</v>
-      </c>
-      <c r="T21" t="s">
-        <v>33</v>
-      </c>
-      <c r="U21" t="s">
-        <v>33</v>
-      </c>
-      <c r="V21" t="s">
-        <v>33</v>
-      </c>
-      <c r="W21" t="s">
-        <v>33</v>
-      </c>
-      <c r="X21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>33</v>
       </c>
       <c r="AB21" t="s">
         <v>33</v>
@@ -8450,7 +8421,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
@@ -8501,7 +8472,7 @@
         <v>33</v>
       </c>
       <c r="R22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="S22" t="s">
         <v>35</v>
@@ -8545,7 +8516,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -8581,7 +8552,7 @@
         <v>33</v>
       </c>
       <c r="M23" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="N23" t="s">
         <v>33</v>
@@ -8596,7 +8567,7 @@
         <v>33</v>
       </c>
       <c r="R23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8640,7 +8611,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -8691,10 +8662,10 @@
         <v>33</v>
       </c>
       <c r="R24" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="S24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T24" t="s">
         <v>33</v>
@@ -8735,10 +8706,10 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -8750,7 +8721,7 @@
         <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="G25" t="s">
         <v>33</v>
@@ -8786,7 +8757,7 @@
         <v>33</v>
       </c>
       <c r="R25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8830,7 +8801,7 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
@@ -8875,16 +8846,16 @@
         <v>33</v>
       </c>
       <c r="P26" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q26" t="s">
         <v>33</v>
       </c>
       <c r="R26" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T26" t="s">
         <v>33</v>
@@ -8925,7 +8896,7 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -8937,13 +8908,13 @@
         <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H27" t="s">
         <v>33</v>
@@ -8958,7 +8929,7 @@
         <v>33</v>
       </c>
       <c r="L27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M27" t="s">
         <v>33</v>
@@ -8976,10 +8947,10 @@
         <v>33</v>
       </c>
       <c r="R27" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="T27" t="s">
         <v>33</v>
@@ -9020,7 +8991,7 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -9065,16 +9036,16 @@
         <v>33</v>
       </c>
       <c r="P28" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q28" t="s">
         <v>33</v>
       </c>
       <c r="R28" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="S28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T28" t="s">
         <v>33</v>
@@ -9115,7 +9086,7 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
@@ -9145,7 +9116,7 @@
         <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L29" t="s">
         <v>33</v>
@@ -9166,10 +9137,10 @@
         <v>33</v>
       </c>
       <c r="R29" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="S29" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="T29" t="s">
         <v>33</v>
@@ -9210,7 +9181,7 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -9261,7 +9232,7 @@
         <v>33</v>
       </c>
       <c r="R30" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -9305,7 +9276,7 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -9400,7 +9371,7 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -9451,7 +9422,7 @@
         <v>33</v>
       </c>
       <c r="R32" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -9495,7 +9466,7 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -9546,7 +9517,7 @@
         <v>33</v>
       </c>
       <c r="R33" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -9590,7 +9561,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -9685,7 +9656,7 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
@@ -9736,7 +9707,7 @@
         <v>33</v>
       </c>
       <c r="R35" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="S35" t="s">
         <v>33</v>
@@ -9780,7 +9751,7 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
         <v>33</v>
@@ -9801,7 +9772,7 @@
         <v>33</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I36" t="s">
         <v>33</v>
@@ -9875,7 +9846,7 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
         <v>33</v>
@@ -9970,7 +9941,7 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
         <v>33</v>
@@ -9985,7 +9956,7 @@
         <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="G38" t="s">
         <v>33</v>
@@ -10006,7 +9977,7 @@
         <v>33</v>
       </c>
       <c r="M38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N38" t="s">
         <v>33</v>
@@ -10021,7 +9992,7 @@
         <v>33</v>
       </c>
       <c r="R38" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="S38" t="s">
         <v>33</v>
@@ -10065,7 +10036,7 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B39" t="s">
         <v>33</v>
@@ -10080,7 +10051,7 @@
         <v>33</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
         <v>33</v>
@@ -10160,7 +10131,7 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B40" t="s">
         <v>33</v>
@@ -10172,10 +10143,10 @@
         <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G40" t="s">
         <v>33</v>
@@ -10211,7 +10182,7 @@
         <v>33</v>
       </c>
       <c r="R40" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -10255,7 +10226,7 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B41" t="s">
         <v>33</v>
@@ -10267,7 +10238,7 @@
         <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
         <v>33</v>
@@ -10350,7 +10321,7 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B42" t="s">
         <v>33</v>
@@ -10362,10 +10333,10 @@
         <v>33</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G42" t="s">
         <v>33</v>
@@ -10401,7 +10372,7 @@
         <v>33</v>
       </c>
       <c r="R42" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="S42" t="s">
         <v>33</v>
@@ -10445,7 +10416,7 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B43" t="s">
         <v>33</v>
@@ -10460,7 +10431,7 @@
         <v>33</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G43" t="s">
         <v>33</v>
@@ -10496,10 +10467,10 @@
         <v>33</v>
       </c>
       <c r="R43" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="S43" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="T43" t="s">
         <v>33</v>
@@ -10540,7 +10511,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B44" t="s">
         <v>33</v>
@@ -10552,7 +10523,7 @@
         <v>33</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F44" t="s">
         <v>33</v>
@@ -10591,7 +10562,7 @@
         <v>33</v>
       </c>
       <c r="R44" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="S44" t="s">
         <v>33</v>
@@ -10635,7 +10606,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B45" t="s">
         <v>33</v>
@@ -10647,7 +10618,7 @@
         <v>33</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F45" t="s">
         <v>33</v>
@@ -10686,10 +10657,10 @@
         <v>33</v>
       </c>
       <c r="R45" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="S45" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T45" t="s">
         <v>33</v>
@@ -10730,7 +10701,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
         <v>33</v>
@@ -10781,7 +10752,7 @@
         <v>33</v>
       </c>
       <c r="R46" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="S46" t="s">
         <v>33</v>
@@ -10825,7 +10796,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B47" t="s">
         <v>33</v>
@@ -10920,31 +10891,31 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="G48" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J48" t="s">
         <v>33</v>
@@ -10953,31 +10924,31 @@
         <v>33</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="O48" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="P48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R48" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="S48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T48" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="U48" t="s">
         <v>33</v>
@@ -10986,25 +10957,25 @@
         <v>33</v>
       </c>
       <c r="W48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="X48" t="s">
         <v>33</v>
       </c>
       <c r="Y48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Z48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA48" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="AB48" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="AC48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AD48" t="s">
         <v>33</v>
@@ -11015,7 +10986,7 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B49" t="s">
         <v>33</v>
@@ -11066,13 +11037,13 @@
         <v>33</v>
       </c>
       <c r="R49" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="S49" t="s">
         <v>33</v>
       </c>
       <c r="T49" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U49" t="s">
         <v>33</v>
@@ -11093,10 +11064,10 @@
         <v>33</v>
       </c>
       <c r="AA49" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="AB49" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="AC49" t="s">
         <v>33</v>
@@ -11110,28 +11081,28 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="F50" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="H50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
         <v>33</v>
@@ -11140,61 +11111,61 @@
         <v>33</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L50" t="s">
+        <v>36</v>
+      </c>
+      <c r="M50" t="s">
+        <v>41</v>
+      </c>
+      <c r="N50" t="s">
+        <v>85</v>
+      </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>36</v>
+      </c>
+      <c r="R50" t="s">
+        <v>140</v>
+      </c>
+      <c r="S50" t="s">
         <v>35</v>
       </c>
-      <c r="M50" t="s">
-        <v>33</v>
-      </c>
-      <c r="N50" t="s">
-        <v>33</v>
-      </c>
-      <c r="O50" t="s">
-        <v>33</v>
-      </c>
-      <c r="P50" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>33</v>
-      </c>
-      <c r="R50" t="s">
-        <v>85</v>
-      </c>
-      <c r="S50" t="s">
-        <v>33</v>
-      </c>
       <c r="T50" t="s">
+        <v>110</v>
+      </c>
+      <c r="U50" t="s">
+        <v>33</v>
+      </c>
+      <c r="V50" t="s">
+        <v>33</v>
+      </c>
+      <c r="W50" t="s">
         <v>35</v>
       </c>
-      <c r="U50" t="s">
-        <v>33</v>
-      </c>
-      <c r="V50" t="s">
-        <v>33</v>
-      </c>
-      <c r="W50" t="s">
-        <v>33</v>
-      </c>
       <c r="X50" t="s">
         <v>33</v>
       </c>
       <c r="Y50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Z50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AA50" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="AB50" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="AC50" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AD50" t="s">
         <v>33</v>
@@ -11205,10 +11176,10 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
         <v>33</v>
@@ -11256,13 +11227,13 @@
         <v>33</v>
       </c>
       <c r="R51" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="S51" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="T51" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U51" t="s">
         <v>33</v>
@@ -11283,10 +11254,10 @@
         <v>33</v>
       </c>
       <c r="AA51" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="AB51" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AC51" t="s">
         <v>33</v>
@@ -11300,7 +11271,7 @@
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B52" t="s">
         <v>33</v>
@@ -11312,7 +11283,7 @@
         <v>33</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="F52" t="s">
         <v>33</v>
@@ -11330,13 +11301,13 @@
         <v>33</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L52" t="s">
         <v>33</v>
       </c>
       <c r="M52" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N52" t="s">
         <v>33</v>
@@ -11351,13 +11322,13 @@
         <v>33</v>
       </c>
       <c r="R52" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="S52" t="s">
         <v>33</v>
       </c>
       <c r="T52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U52" t="s">
         <v>33</v>
@@ -11378,10 +11349,10 @@
         <v>33</v>
       </c>
       <c r="AA52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AB52" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="AC52" t="s">
         <v>33</v>
@@ -11395,7 +11366,7 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B53" t="s">
         <v>33</v>
@@ -11413,7 +11384,7 @@
         <v>33</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="H53" t="s">
         <v>33</v>
@@ -11446,13 +11417,13 @@
         <v>33</v>
       </c>
       <c r="R53" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="S53" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="T53" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U53" t="s">
         <v>33</v>
@@ -11473,7 +11444,7 @@
         <v>33</v>
       </c>
       <c r="AA53" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="AB53" t="s">
         <v>33</v>
@@ -11490,7 +11461,7 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
         <v>33</v>
@@ -11523,7 +11494,7 @@
         <v>33</v>
       </c>
       <c r="L54" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M54" t="s">
         <v>33</v>
@@ -11585,7 +11556,7 @@
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B55" t="s">
         <v>33</v>
@@ -11663,7 +11634,7 @@
         <v>33</v>
       </c>
       <c r="AA55" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="AB55" t="s">
         <v>33</v>
@@ -11680,7 +11651,7 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>33</v>
@@ -11731,10 +11702,10 @@
         <v>33</v>
       </c>
       <c r="R56" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="S56" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="T56" t="s">
         <v>33</v>
@@ -11758,7 +11729,7 @@
         <v>33</v>
       </c>
       <c r="AA56" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AB56" t="s">
         <v>33</v>
@@ -11775,7 +11746,7 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B57" t="s">
         <v>33</v>
@@ -11826,7 +11797,7 @@
         <v>33</v>
       </c>
       <c r="R57" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="S57" t="s">
         <v>33</v>
@@ -11853,7 +11824,7 @@
         <v>33</v>
       </c>
       <c r="AA57" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="AB57" t="s">
         <v>33</v>
@@ -11870,7 +11841,7 @@
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B58" t="s">
         <v>33</v>
@@ -11921,10 +11892,10 @@
         <v>33</v>
       </c>
       <c r="R58" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="S58" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T58" t="s">
         <v>33</v>
@@ -11948,7 +11919,7 @@
         <v>33</v>
       </c>
       <c r="AA58" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AB58" t="s">
         <v>33</v>
@@ -11965,100 +11936,296 @@
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" t="s">
+        <v>33</v>
+      </c>
+      <c r="I59" t="s">
+        <v>33</v>
+      </c>
+      <c r="J59" t="s">
+        <v>33</v>
+      </c>
+      <c r="K59" t="s">
+        <v>33</v>
+      </c>
+      <c r="L59" t="s">
+        <v>33</v>
+      </c>
+      <c r="M59" t="s">
+        <v>33</v>
+      </c>
+      <c r="N59" t="s">
+        <v>33</v>
+      </c>
+      <c r="O59" t="s">
+        <v>33</v>
+      </c>
+      <c r="P59" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>33</v>
+      </c>
+      <c r="R59" t="s">
+        <v>157</v>
+      </c>
+      <c r="S59" t="s">
+        <v>33</v>
+      </c>
+      <c r="T59" t="s">
+        <v>33</v>
+      </c>
+      <c r="U59" t="s">
+        <v>33</v>
+      </c>
+      <c r="V59" t="s">
+        <v>33</v>
+      </c>
+      <c r="W59" t="s">
+        <v>33</v>
+      </c>
+      <c r="X59" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" t="s">
+        <v>33</v>
+      </c>
+      <c r="J60" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60" t="s">
+        <v>33</v>
+      </c>
+      <c r="L60" t="s">
+        <v>33</v>
+      </c>
+      <c r="M60" t="s">
+        <v>33</v>
+      </c>
+      <c r="N60" t="s">
+        <v>33</v>
+      </c>
+      <c r="O60" t="s">
+        <v>33</v>
+      </c>
+      <c r="P60" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>33</v>
+      </c>
+      <c r="R60" t="s">
+        <v>33</v>
+      </c>
+      <c r="S60" t="s">
+        <v>33</v>
+      </c>
+      <c r="T60" t="s">
+        <v>33</v>
+      </c>
+      <c r="U60" t="s">
+        <v>33</v>
+      </c>
+      <c r="V60" t="s">
+        <v>33</v>
+      </c>
+      <c r="W60" t="s">
+        <v>33</v>
+      </c>
+      <c r="X60" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>159</v>
       </c>
-      <c r="B59" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" t="s">
-        <v>33</v>
-      </c>
-      <c r="E59" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59" t="s">
-        <v>33</v>
-      </c>
-      <c r="G59" t="s">
-        <v>33</v>
-      </c>
-      <c r="H59" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" t="s">
-        <v>33</v>
-      </c>
-      <c r="J59" t="s">
-        <v>33</v>
-      </c>
-      <c r="K59" t="s">
-        <v>33</v>
-      </c>
-      <c r="L59" t="s">
-        <v>33</v>
-      </c>
-      <c r="M59" t="s">
-        <v>33</v>
-      </c>
-      <c r="N59" t="s">
-        <v>33</v>
-      </c>
-      <c r="O59" t="s">
-        <v>33</v>
-      </c>
-      <c r="P59" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>33</v>
-      </c>
-      <c r="R59" t="s">
-        <v>33</v>
-      </c>
-      <c r="S59" t="s">
-        <v>33</v>
-      </c>
-      <c r="T59" t="s">
-        <v>33</v>
-      </c>
-      <c r="U59" t="s">
-        <v>33</v>
-      </c>
-      <c r="V59" t="s">
-        <v>33</v>
-      </c>
-      <c r="W59" t="s">
-        <v>33</v>
-      </c>
-      <c r="X59" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE59" t="s">
+      <c r="B61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" t="s">
+        <v>33</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" t="s">
+        <v>33</v>
+      </c>
+      <c r="I61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" t="s">
+        <v>33</v>
+      </c>
+      <c r="K61" t="s">
+        <v>33</v>
+      </c>
+      <c r="L61" t="s">
+        <v>33</v>
+      </c>
+      <c r="M61" t="s">
+        <v>33</v>
+      </c>
+      <c r="N61" t="s">
+        <v>33</v>
+      </c>
+      <c r="O61" t="s">
+        <v>33</v>
+      </c>
+      <c r="P61" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>33</v>
+      </c>
+      <c r="R61" t="s">
+        <v>33</v>
+      </c>
+      <c r="S61" t="s">
+        <v>33</v>
+      </c>
+      <c r="T61" t="s">
+        <v>33</v>
+      </c>
+      <c r="U61" t="s">
+        <v>33</v>
+      </c>
+      <c r="V61" t="s">
+        <v>33</v>
+      </c>
+      <c r="W61" t="s">
+        <v>33</v>
+      </c>
+      <c r="X61" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE61" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="W2:AE2"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/res/tabela da comunidade.xlsx
+++ b/res/tabela da comunidade.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_Zoo-Rebio/ZooRebio3-23_24/rebio23-part/res/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_B992312702B166F0E476389F13FD156A6ADA3413" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6581421A-5591-4556-A5C5-D1B7D845147B}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-22425" windowWidth="21840" windowHeight="37920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-22425" windowWidth="21840" windowHeight="37920" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
-    <sheet name="tabela_final" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tabela_final" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
   <si>
     <t>Variable</t>
   </si>
@@ -567,19 +560,505 @@
   </si>
   <si>
     <t>Caiana Stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_chuvoso_Ponto10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_chuvoso_Ponto5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_chuvoso_Ponto6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_chuvoso_Ponto7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_chuvoso_Ponto8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_chuvoso_Ponto9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_seco_Ponto10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_seco_Ponto5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_seco_Ponto6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_seco_Ponto7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_seco_Ponto8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barro.Branco_seco_Ponto9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_chuvoso_Ponto20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caiana_seco_Ponto20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alo.dadayi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3 (6.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alo.hamulata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 (1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alonella.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bdelloidea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9 (1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 (0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (0.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 (0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9 (0.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9 (1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 (0.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bra.patulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cephalodella.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colurella.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copepodite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1 (14.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9 (0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chydorus.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2 (3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9 (0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dicranophoroides.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dia.birgei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dia.spinulosum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dis.aculeata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euc.dilatata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fil.longiseta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ily.spinifer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.aculeata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.bulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.cornuta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.crepida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.curvicornis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.furcata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecane.sp1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.leontina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.lunaris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.luna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.monostyla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecane.sp2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.papuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lec.quadridentata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecane.sp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leydigia.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lepadella.sp1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lepadella.sp2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lep.ovalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lep.patella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesocyclops.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrocyclops.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrochaetus.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrothrix.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mac.mira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mac.laticornis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 (0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moi.minuta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myt.crassipes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mytilina.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myt.bisulcata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nauplii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 (1.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2 (2.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 (0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4 (8.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notodiaptomus.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paracyclops.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7 (1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pla.quadricornis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (1.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polyarthra.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pol.bicerca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pol.dolichoptera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pol.vulgaris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tes.patina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tes.mucronata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trichocerca.sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tri.tetractis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -602,15 +1081,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -628,10 +1104,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -912,5613 +1384,5613 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE59"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>187</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>189</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>191</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>193</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>196</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>197</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="V1" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="Z1" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="AA1" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="AB1" t="s">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="AD1" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="AE1" t="s">
-        <v>30</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="T2" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="U2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE2" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R3" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="S3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="V3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE3" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>224</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE4" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>228</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>230</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>232</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>234</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>235</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>236</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>237</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>238</v>
       </c>
       <c r="L5" t="s">
-        <v>57</v>
+        <v>239</v>
       </c>
       <c r="M5" t="s">
-        <v>58</v>
+        <v>240</v>
       </c>
       <c r="N5" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>243</v>
       </c>
       <c r="Q5" t="s">
-        <v>62</v>
+        <v>244</v>
       </c>
       <c r="R5" t="s">
-        <v>63</v>
+        <v>245</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>246</v>
       </c>
       <c r="T5" t="s">
-        <v>65</v>
+        <v>247</v>
       </c>
       <c r="U5" t="s">
-        <v>66</v>
+        <v>248</v>
       </c>
       <c r="V5" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="X5" t="s">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="Y5" t="s">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="Z5" t="s">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="AA5" t="s">
-        <v>70</v>
+        <v>252</v>
       </c>
       <c r="AB5" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="AC5" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
       <c r="AD5" t="s">
-        <v>72</v>
+        <v>254</v>
       </c>
       <c r="AE5" t="s">
-        <v>66</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R6" t="s">
-        <v>55</v>
+        <v>237</v>
       </c>
       <c r="S6" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE6" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R8" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="S8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE8" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L9" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="M9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N9" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="O9" t="s">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="P9" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R9" t="s">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="S9" t="s">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="T9" t="s">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="U9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W9" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="X9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z9" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="AA9" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="AB9" t="s">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AC9" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="AD9" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE9" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>269</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R10" t="s">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="S10" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="T10" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="U10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE10" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE11" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P12" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R12" t="s">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="S12" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T12" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="U12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA12" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="AB12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE12" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA13" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="AB13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE13" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>275</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE14" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE15" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE16" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>278</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R17" t="s">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="S17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE17" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R18" t="s">
-        <v>99</v>
+        <v>281</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE18" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>282</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L19" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R19" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="S19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W19" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="X19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="AB19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE19" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R20" t="s">
-        <v>102</v>
+        <v>284</v>
       </c>
       <c r="S20" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE20" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>285</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R21" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="S21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE21" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>286</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R22" t="s">
-        <v>105</v>
+        <v>287</v>
       </c>
       <c r="S22" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE22" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE23" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>289</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE24" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>252</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R25" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="S25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE25" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P26" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="Q26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R26" t="s">
-        <v>110</v>
+        <v>292</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE26" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L27" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="M27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R27" t="s">
-        <v>112</v>
+        <v>294</v>
       </c>
       <c r="S27" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="T27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE27" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE28" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE29" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
-        <v>115</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R30" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="S30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE30" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE31" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE32" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R33" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="S33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE34" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE35" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H36" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE36" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE37" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F38" t="s">
-        <v>124</v>
+        <v>306</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R38" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="S38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE38" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="G39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE39" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F40" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE40" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE41" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="G42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R42" t="s">
-        <v>129</v>
+        <v>311</v>
       </c>
       <c r="S42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE42" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="G43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R43" t="s">
-        <v>131</v>
+        <v>313</v>
       </c>
       <c r="S43" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="T43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE43" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R44" t="s">
-        <v>133</v>
+        <v>315</v>
       </c>
       <c r="S44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE44" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE45" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
-        <v>135</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE46" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE47" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="F48" t="s">
-        <v>139</v>
+        <v>321</v>
       </c>
       <c r="G48" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="I48" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="J48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="M48" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="N48" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="O48" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="P48" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="Q48" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="R48" t="s">
-        <v>140</v>
+        <v>322</v>
       </c>
       <c r="S48" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="T48" t="s">
-        <v>110</v>
+        <v>292</v>
       </c>
       <c r="U48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W48" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="X48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y48" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="Z48" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="AA48" t="s">
-        <v>141</v>
+        <v>323</v>
       </c>
       <c r="AB48" t="s">
-        <v>142</v>
+        <v>324</v>
       </c>
       <c r="AC48" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="AD48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE48" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R49" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="S49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T49" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="U49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA49" t="s">
-        <v>144</v>
+        <v>326</v>
       </c>
       <c r="AB49" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="AC49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE49" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F50" t="s">
-        <v>146</v>
+        <v>328</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L50" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="M50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R50" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="S50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T50" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="U50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA50" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="AB50" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="AC50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE50" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>330</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R51" t="s">
-        <v>149</v>
+        <v>331</v>
       </c>
       <c r="S51" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="T51" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="U51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE51" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>332</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M52" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="N52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE52" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA53" t="s">
-        <v>91</v>
+        <v>273</v>
       </c>
       <c r="AB53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE53" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE54" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA55" t="s">
-        <v>154</v>
+        <v>336</v>
       </c>
       <c r="AB55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE55" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
-        <v>155</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R56" t="s">
-        <v>85</v>
+        <v>267</v>
       </c>
       <c r="S56" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="T56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA56" t="s">
-        <v>35</v>
+        <v>217</v>
       </c>
       <c r="AB56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE56" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R57" t="s">
-        <v>157</v>
+        <v>339</v>
       </c>
       <c r="S57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE57" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>340</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE58" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
-        <v>159</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="D59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="G59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="I59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="J59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="K59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="L59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="M59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="N59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="O59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="P59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Q59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="R59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="S59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="T59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="U59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="V59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="W59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="X59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Y59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="Z59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AA59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AB59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AC59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AD59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="AE59" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -6528,15 +7000,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{768C672F-8BDD-430E-9621-0F0E0D5E9FE7}">
-  <dimension ref="A1:AE61"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C1" s="1"/>
@@ -6550,71 +7022,71 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2" t="s">
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>179</v>
       </c>
@@ -6709,7 +7181,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -6804,7 +7276,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -6899,7 +7371,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -6994,7 +7466,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -7089,7 +7561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -7184,7 +7656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>74</v>
       </c>
@@ -7279,7 +7751,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -7374,7 +7846,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -7469,7 +7941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -7564,7 +8036,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -7659,7 +8131,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -7754,7 +8226,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -7849,7 +8321,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -7944,7 +8416,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -8039,7 +8511,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -8134,7 +8606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -8229,7 +8701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -8324,7 +8796,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>100</v>
       </c>
@@ -8419,7 +8891,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -8514,7 +8986,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -8609,7 +9081,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>104</v>
       </c>
@@ -8704,7 +9176,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -8799,7 +9271,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -8894,7 +9366,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -8989,7 +9461,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>109</v>
       </c>
@@ -9084,7 +9556,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>111</v>
       </c>
@@ -9179,7 +9651,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>113</v>
       </c>
@@ -9274,7 +9746,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>114</v>
       </c>
@@ -9369,7 +9841,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -9464,7 +9936,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>116</v>
       </c>
@@ -9559,7 +10031,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>117</v>
       </c>
@@ -9654,7 +10126,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -9749,7 +10221,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>119</v>
       </c>
@@ -9844,7 +10316,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -9939,7 +10411,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -10034,7 +10506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -10129,7 +10601,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -10224,7 +10696,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>125</v>
       </c>
@@ -10319,7 +10791,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>126</v>
       </c>
@@ -10414,7 +10886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>127</v>
       </c>
@@ -10509,7 +10981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -10604,7 +11076,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>130</v>
       </c>
@@ -10699,7 +11171,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -10794,7 +11266,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>134</v>
       </c>
@@ -10889,7 +11361,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -10984,7 +11456,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>136</v>
       </c>
@@ -11079,7 +11551,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>137</v>
       </c>
@@ -11174,7 +11646,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>143</v>
       </c>
@@ -11269,7 +11741,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>145</v>
       </c>
@@ -11364,7 +11836,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>147</v>
       </c>
@@ -11459,7 +11931,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -11554,7 +12026,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>151</v>
       </c>
@@ -11649,7 +12121,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>152</v>
       </c>
@@ -11744,7 +12216,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>153</v>
       </c>
@@ -11839,7 +12311,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>155</v>
       </c>
@@ -11934,7 +12406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>156</v>
       </c>
@@ -12029,7 +12501,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>158</v>
       </c>
@@ -12124,7 +12596,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>159</v>
       </c>
@@ -12227,5 +12699,6 @@
     <mergeCell ref="W2:AE2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>